--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_248_R25.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_248_R25.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.714</v>
+        <v>5.1831</v>
       </c>
       <c r="E2" t="n">
-        <v>4.829</v>
+        <v>4.6677</v>
       </c>
       <c r="F2" t="n">
-        <v>0.885</v>
+        <v>0.5153</v>
       </c>
       <c r="G2" t="n">
         <v>3.5202</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>2.0493</v>
+        <v>1.5184</v>
       </c>
       <c r="T2" t="n">
-        <v>1.1404</v>
+        <v>0.9792</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9089</v>
+        <v>0.5392</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.5177</v>
+        <v>3.1321</v>
       </c>
       <c r="E3" t="n">
-        <v>4.8078</v>
+        <v>5.5902</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.2901</v>
+        <v>-2.4581</v>
       </c>
       <c r="G3" t="n">
         <v>2.4137</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0532</v>
+        <v>0.5612</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5895</v>
+        <v>0.1928</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3322</v>
+        <v>2.972</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4728</v>
+        <v>2.9446</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1406</v>
+        <v>0.0274</v>
       </c>
       <c r="G4" t="n">
         <v>1.8596</v>
@@ -766,13 +766,13 @@
         <v>0.6959</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1357</v>
+        <v>0.5041</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4323</v>
+        <v>0.0395</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2965</v>
+        <v>0.4646</v>
       </c>
       <c r="V4" t="n">
         <v>1.0722</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.1631</v>
+        <v>2.0116</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2685</v>
+        <v>1.4621</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.1054</v>
+        <v>0.5495</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.8848</v>
+        <v>-3.3657</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9953</v>
+        <v>0.228</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1105</v>
+        <v>-3.5937</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7844</v>
+        <v>-2.7472</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5406</v>
+        <v>0.6827</v>
       </c>
       <c r="L5" t="n">
-        <v>1.325</v>
+        <v>-3.4299</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6691</v>
+        <v>-0.6185</v>
       </c>
       <c r="N5" t="n">
         <v>-0.4547</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2144</v>
+        <v>-0.1638</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7437</v>
+        <v>0.1582</v>
       </c>
       <c r="T5" t="n">
-        <v>3.7314</v>
+        <v>0.0081</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0123</v>
+        <v>0.15</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>5.2192</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>5.361</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2538</v>
+        <v>0.7971</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8724</v>
+        <v>-0.0747</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3815</v>
+        <v>0.8718</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.3657</v>
+        <v>0.4718</v>
       </c>
       <c r="H6" t="n">
-        <v>0.228</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.5937</v>
+        <v>0.4718</v>
       </c>
       <c r="J6" t="n">
-        <v>-2.7472</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6827</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.4299</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6185</v>
+        <v>0.4718</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4547</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1638</v>
+        <v>0.4718</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5996</v>
+        <v>0.0934</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5816</v>
+        <v>-0.0747</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.018</v>
+        <v>0.168</v>
       </c>
       <c r="V6" t="n">
-        <v>5.2192</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>5.361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6963</v>
+        <v>0.4342</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0747</v>
+        <v>1.338</v>
       </c>
       <c r="F7" t="n">
-        <v>0.771</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4718</v>
+        <v>-0.8848</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0.9953</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4718</v>
+        <v>0.1105</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.7844</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>-0.5406</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.325</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4718</v>
+        <v>-1.6691</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.4547</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4718</v>
+        <v>-1.2144</v>
       </c>
       <c r="P7" t="n">
-        <v>0.232</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0075</v>
+        <v>2.0148</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0747</v>
+        <v>1.8009</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0672</v>
+        <v>0.2139</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0994</v>
+        <v>-0.0515</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0964</v>
+        <v>0.0216</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1958</v>
+        <v>-0.073</v>
       </c>
       <c r="G8" t="n">
         <v>0.6842</v>
@@ -1078,13 +1078,13 @@
         <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5597</v>
+        <v>0.4088</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.1729</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8505</v>
+        <v>0.5816</v>
       </c>
       <c r="V8" t="n">
         <v>-1.6083</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-0.3542</v>
       </c>
       <c r="E9" t="n">
         <v>1.4843</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0402</v>
+        <v>-1.8386</v>
       </c>
       <c r="G9" t="n">
         <v>2.2192</v>
@@ -1156,13 +1156,13 @@
         <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7029</v>
+        <v>-0.5012</v>
       </c>
       <c r="T9" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.188</v>
+        <v>0.0136</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6083</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5763</v>
+        <v>-0.3576</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.208</v>
+        <v>-0.0901</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3683</v>
+        <v>-0.2675</v>
       </c>
       <c r="G10" t="n">
         <v>-0.435</v>
@@ -1234,13 +1234,13 @@
         <v>0.232</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2315</v>
+        <v>-0.0127</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0672</v>
+        <v>0.168</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>G. RADZEVICIUS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6972</v>
+        <v>-0.6163</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1426</v>
+        <v>0.438</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8397</v>
+        <v>-1.0544</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3889</v>
+        <v>-2.4027</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5533</v>
+        <v>-0.6494</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1644</v>
+        <v>-1.7533</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1134</v>
+        <v>-0.2044</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.7023</v>
+        <v>0.7058</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5889</v>
+        <v>-0.9102</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2755</v>
+        <v>-2.1983</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.851</v>
+        <v>-1.3552</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5756</v>
+        <v>-0.8431</v>
       </c>
       <c r="P11" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3</v>
+        <v>0.3224</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1142</v>
+        <v>0.1063</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1858</v>
+        <v>0.2161</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>G. RADZEVICIUS</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.1628</v>
+        <v>-1.2026</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.1085</v>
+        <v>-0.3293</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0544</v>
+        <v>-0.8733</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.4027</v>
+        <v>-0.3889</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6494</v>
+        <v>-1.5533</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7533</v>
+        <v>1.1644</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2044</v>
+        <v>-0.1134</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7058</v>
+        <v>-0.7023</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.9102</v>
+        <v>0.5889</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.1983</v>
+        <v>-0.2755</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3552</v>
+        <v>-0.851</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8431</v>
+        <v>0.5756</v>
       </c>
       <c r="P12" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.224</v>
+        <v>-0.2054</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>-0.3576</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2161</v>
+        <v>0.1522</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5361</v>
+        <v>-1.0722</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5361</v>
+        <v>0.1418</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7817</v>
+        <v>-1.5719</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9644</v>
+        <v>1.275</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7461</v>
+        <v>-2.8469</v>
       </c>
       <c r="G13" t="n">
         <v>-1.4904</v>
@@ -1468,13 +1468,13 @@
         <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0593</v>
+        <v>0.1505</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2047</v>
+        <v>0.5153</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.264</v>
+        <v>-0.3648</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.0026</v>
+        <v>10.376</v>
       </c>
       <c r="E14" t="n">
-        <v>18.35420000000001</v>
+        <v>18.7274</v>
       </c>
       <c r="F14" t="n">
         <v>-8.3515</v>
@@ -1513,7 +1513,7 @@
         <v>2.201200000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>6.668199999999999</v>
+        <v>6.668200000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-4.466900000000001</v>
@@ -1525,7 +1525,7 @@
         <v>14.877</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2184999999999998</v>
+        <v>-0.2184999999999997</v>
       </c>
       <c r="M14" t="n">
         <v>-12.4574</v>
@@ -1540,19 +1540,19 @@
         <v>1.1598</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.2782</v>
+        <v>-9.278200000000002</v>
       </c>
       <c r="R14" t="n">
         <v>10.4381</v>
       </c>
       <c r="S14" t="n">
-        <v>4.639</v>
+        <v>5.0125</v>
       </c>
       <c r="T14" t="n">
-        <v>1.967999999999999</v>
+        <v>2.3412</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6709</v>
+        <v>2.6708</v>
       </c>
       <c r="V14" t="n">
         <v>2.0026</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4666</v>
+        <v>2.6078</v>
       </c>
       <c r="E15" t="n">
-        <v>1.0422</v>
+        <v>6.8426</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4245</v>
+        <v>-4.2348</v>
       </c>
       <c r="G15" t="n">
-        <v>0.08989999999999999</v>
+        <v>3.1294</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3542</v>
+        <v>2.0924</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2643</v>
+        <v>1.0371</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5546</v>
+        <v>5.9537</v>
       </c>
       <c r="K15" t="n">
-        <v>0.5546</v>
+        <v>4.8566</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.0971</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4647</v>
+        <v>-2.8243</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2004</v>
+        <v>-2.7643</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2643</v>
+        <v>-0.06</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>-3.4793</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1448</v>
+        <v>-0.7951</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4876</v>
+        <v>-0.3692</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6572</v>
+        <v>-0.4259</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>3.7527</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>5.8971</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3667</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0169</v>
+        <v>0.5704</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.6502</v>
+        <v>0.29</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1294</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0924</v>
+        <v>0.3542</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0371</v>
+        <v>-0.2643</v>
       </c>
       <c r="J16" t="n">
-        <v>5.9537</v>
+        <v>0.5546</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8566</v>
+        <v>0.5546</v>
       </c>
       <c r="L16" t="n">
-        <v>1.0971</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8243</v>
+        <v>-0.4647</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.7643</v>
+        <v>-0.2004</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.06</v>
+        <v>-0.2643</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.4793</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>0.232</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0362</v>
+        <v>0.5386</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1949</v>
+        <v>0.0158</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8413</v>
+        <v>0.5228</v>
       </c>
       <c r="V16" t="n">
-        <v>3.7527</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>5.8971</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8583</v>
+        <v>0.3422</v>
       </c>
       <c r="E17" t="n">
-        <v>3.0579</v>
+        <v>-0.09859999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.1996</v>
+        <v>0.4408</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.143</v>
+        <v>-0.3985</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.9557</v>
+        <v>-0.6494</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1873</v>
+        <v>0.2509</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4875</v>
+        <v>1.2138</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1148</v>
+        <v>0.5917</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.6222</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6555</v>
+        <v>-1.6123</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0705</v>
+        <v>-1.241</v>
       </c>
       <c r="O17" t="n">
-        <v>0.415</v>
+        <v>-0.3713</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
         <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0735</v>
+        <v>0.1298</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4732</v>
+        <v>-0.6012</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3998</v>
+        <v>0.731</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>2.0026</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.0722</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5717</v>
+        <v>-0.8833</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0194</v>
+        <v>-1.6999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5524</v>
+        <v>0.8166</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3985</v>
+        <v>-0.1761</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6494</v>
+        <v>-0.929</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2509</v>
+        <v>0.7529</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2138</v>
+        <v>-0.2219</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5917</v>
+        <v>0.4908</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6222</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6123</v>
+        <v>0.0458</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.241</v>
+        <v>-1.4199</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.3713</v>
+        <v>1.4657</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3593</v>
+        <v>-0.4031</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4832</v>
+        <v>-0.3183</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8426</v>
+        <v>-0.0848</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0026</v>
+        <v>-0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5027</v>
+        <v>-0.8863</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0521</v>
+        <v>1.2373</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.5548</v>
+        <v>-2.1236</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9166</v>
+        <v>0.0334</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7033</v>
+        <v>-0.144</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6199</v>
+        <v>0.1774</v>
       </c>
       <c r="J19" t="n">
-        <v>1.814</v>
+        <v>1.245</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6519</v>
+        <v>0.0672</v>
       </c>
       <c r="L19" t="n">
-        <v>2.4659</v>
+        <v>1.1778</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8974</v>
+        <v>-1.2116</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0514</v>
+        <v>-0.2112</v>
       </c>
       <c r="O19" t="n">
-        <v>0.154</v>
+        <v>-1.0004</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2095</v>
+        <v>-0.3115</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1142</v>
+        <v>-0.0077</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0953</v>
+        <v>-0.3038</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.3969</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.6805</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7203</v>
+        <v>-0.9833</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6428</v>
+        <v>1.1707</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3631</v>
+        <v>-2.1539</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1539</v>
+        <v>-2.143</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6424</v>
+        <v>-1.9557</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4885</v>
+        <v>-0.1873</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8377</v>
+        <v>-0.4875</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6069</v>
+        <v>0.1148</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2308</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9916</v>
+        <v>-1.6555</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2493</v>
+        <v>-2.0705</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2578</v>
+        <v>0.415</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.654</v>
+        <v>0.232</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>0.586</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4591</v>
+        <v>-0.3541</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
         <v>-1.0722</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7342</v>
+        <v>-1.2035</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6475</v>
+        <v>0.8787</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3817</v>
+        <v>-2.0821</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0334</v>
+        <v>-0.1539</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.144</v>
+        <v>-0.6424</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1774</v>
+        <v>0.4885</v>
       </c>
       <c r="J21" t="n">
-        <v>1.245</v>
+        <v>1.8377</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0672</v>
+        <v>1.6069</v>
       </c>
       <c r="L21" t="n">
-        <v>1.1778</v>
+        <v>0.2308</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.2116</v>
+        <v>-1.9916</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2112</v>
+        <v>-2.2493</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0004</v>
+        <v>0.2578</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1593</v>
+        <v>-1.1371</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5975</v>
+        <v>-0.959</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5619</v>
+        <v>-0.1781</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8649</v>
+        <v>-1.3397</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0538</v>
+        <v>0.9341</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1889</v>
+        <v>-2.2738</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1761</v>
+        <v>0.9166</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.929</v>
+        <v>-1.7033</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7529</v>
+        <v>2.6199</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.2219</v>
+        <v>1.814</v>
       </c>
       <c r="K22" t="n">
-        <v>0.4908</v>
+        <v>-0.6519</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7127</v>
+        <v>2.4659</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0458</v>
+        <v>-0.8974</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4199</v>
+        <v>-1.0514</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4657</v>
+        <v>0.154</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>-0.232</v>
       </c>
       <c r="Q22" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3847</v>
+        <v>0.3725</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>-0.0037</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7125</v>
+        <v>0.3763</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5361</v>
+        <v>-2.3969</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5361</v>
+        <v>-2.6805</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5686</v>
+        <v>-1.9281</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4259</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9945</v>
+        <v>-2.5899</v>
       </c>
       <c r="G23" t="n">
         <v>-1.2218</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2204</v>
+        <v>-0.5799</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4832</v>
+        <v>-0.2473</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7371</v>
+        <v>-0.3325</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7501</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.8753</v>
+        <v>-4.2297</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.4993</v>
+        <v>-2.1455</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3759</v>
+        <v>-2.0842</v>
       </c>
       <c r="G24" t="n">
         <v>-2.2773</v>
@@ -2326,13 +2326,13 @@
         <v>0.4639</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9717</v>
+        <v>-0.3262</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1202</v>
+        <v>-0.7664</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1485</v>
+        <v>0.4402</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9304</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.0027</v>
+        <v>-7.6435</v>
       </c>
       <c r="E25" t="n">
-        <v>8.351600000000001</v>
+        <v>8.351599999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.354</v>
+        <v>-15.9949</v>
       </c>
       <c r="G25" t="n">
         <v>-2.2013</v>
@@ -2374,16 +2374,16 @@
         <v>-6.668</v>
       </c>
       <c r="I25" t="n">
-        <v>4.466900000000001</v>
+        <v>4.4669</v>
       </c>
       <c r="J25" t="n">
         <v>12.4573</v>
       </c>
       <c r="K25" t="n">
-        <v>8.209</v>
+        <v>8.209000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>4.2484</v>
+        <v>4.248399999999999</v>
       </c>
       <c r="M25" t="n">
         <v>-14.6586</v>
@@ -2404,13 +2404,13 @@
         <v>9.2782</v>
       </c>
       <c r="S25" t="n">
-        <v>-4.6392</v>
+        <v>-2.28</v>
       </c>
       <c r="T25" t="n">
         <v>-2.671</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.9681</v>
+        <v>0.3911000000000001</v>
       </c>
       <c r="V25" t="n">
         <v>-2.0026</v>
